--- a/artfynd/A 24054-2025 artfynd.xlsx
+++ b/artfynd/A 24054-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,38 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126019996</v>
+        <v>126022261</v>
       </c>
       <c r="B2" t="n">
-        <v>57651</v>
+        <v>98334</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>70</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549046</v>
+        <v>549227</v>
       </c>
       <c r="R2" t="n">
-        <v>6943812</v>
+        <v>6943821</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +750,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,37 +776,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126020940</v>
+        <v>126022283</v>
       </c>
       <c r="B3" t="n">
-        <v>92510</v>
+        <v>98334</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -821,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549196</v>
+        <v>549248</v>
       </c>
       <c r="R3" t="n">
-        <v>6943799</v>
+        <v>6943846</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,37 +877,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126022283</v>
+        <v>126020940</v>
       </c>
       <c r="B4" t="n">
-        <v>98332</v>
+        <v>92518</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -922,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549248</v>
+        <v>549196</v>
       </c>
       <c r="R4" t="n">
-        <v>6943846</v>
+        <v>6943799</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,37 +978,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126022261</v>
+        <v>126019996</v>
       </c>
       <c r="B5" t="n">
-        <v>98332</v>
+        <v>57651</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>70</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1023,10 +1018,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>549227</v>
+        <v>549046</v>
       </c>
       <c r="R5" t="n">
-        <v>6943821</v>
+        <v>6943812</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1059,6 +1054,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,7 +1088,7 @@
         <v>126022879</v>
       </c>
       <c r="B6" t="n">
-        <v>92510</v>
+        <v>92518</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>126020676</v>
       </c>
       <c r="B8" t="n">
-        <v>92510</v>
+        <v>92518</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1384,10 +1384,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126020477</v>
+        <v>126023583</v>
       </c>
       <c r="B9" t="n">
-        <v>92510</v>
+        <v>97212</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1395,38 +1395,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>549094</v>
+        <v>549060</v>
       </c>
       <c r="R9" t="n">
-        <v>6943793</v>
+        <v>6943945</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,11 +1455,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1490,10 +1481,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126023583</v>
+        <v>126020477</v>
       </c>
       <c r="B10" t="n">
-        <v>97210</v>
+        <v>92518</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1501,34 +1492,38 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>549060</v>
+        <v>549094</v>
       </c>
       <c r="R10" t="n">
-        <v>6943945</v>
+        <v>6943793</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1561,6 +1556,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1590,7 +1590,7 @@
         <v>126021032</v>
       </c>
       <c r="B11" t="n">
-        <v>92510</v>
+        <v>92518</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>126022352</v>
       </c>
       <c r="B12" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>126020410</v>
       </c>
       <c r="B13" t="n">
-        <v>92510</v>
+        <v>92518</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1910,37 +1910,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126023708</v>
+        <v>126021074</v>
       </c>
       <c r="B14" t="n">
-        <v>98332</v>
+        <v>92518</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1949,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>549056</v>
+        <v>549255</v>
       </c>
       <c r="R14" t="n">
-        <v>6943960</v>
+        <v>6943783</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1985,6 +1990,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2011,42 +2021,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126021074</v>
+        <v>126023708</v>
       </c>
       <c r="B15" t="n">
-        <v>92510</v>
+        <v>98334</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2055,10 +2060,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>549255</v>
+        <v>549056</v>
       </c>
       <c r="R15" t="n">
-        <v>6943783</v>
+        <v>6943960</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2091,11 +2096,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2229,38 +2229,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126022148</v>
+        <v>126022598</v>
       </c>
       <c r="B17" t="n">
-        <v>58020</v>
+        <v>98334</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>60</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2269,10 +2268,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>549228</v>
+        <v>549225</v>
       </c>
       <c r="R17" t="n">
-        <v>6943849</v>
+        <v>6943798</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2331,37 +2330,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126022598</v>
+        <v>126022148</v>
       </c>
       <c r="B18" t="n">
-        <v>98332</v>
+        <v>58020</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>60</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2370,10 +2370,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>549225</v>
+        <v>549228</v>
       </c>
       <c r="R18" t="n">
-        <v>6943798</v>
+        <v>6943849</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2731,7 +2731,7 @@
         <v>126022476</v>
       </c>
       <c r="B22" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>126023779</v>
       </c>
       <c r="B24" t="n">
-        <v>98353</v>
+        <v>98355</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3027,49 +3027,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126023135</v>
+        <v>126021627</v>
       </c>
       <c r="B25" t="n">
-        <v>92510</v>
+        <v>78968</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>549141</v>
+        <v>549225</v>
       </c>
       <c r="R25" t="n">
-        <v>6943883</v>
+        <v>6943798</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3102,11 +3098,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3133,38 +3124,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126023512</v>
+        <v>126023135</v>
       </c>
       <c r="B26" t="n">
-        <v>57651</v>
+        <v>92518</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3173,10 +3163,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>549050</v>
+        <v>549141</v>
       </c>
       <c r="R26" t="n">
-        <v>6943946</v>
+        <v>6943883</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3213,7 +3203,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3240,10 +3230,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126021627</v>
+        <v>126023512</v>
       </c>
       <c r="B27" t="n">
-        <v>78968</v>
+        <v>57651</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3251,34 +3241,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>549225</v>
+        <v>549050</v>
       </c>
       <c r="R27" t="n">
-        <v>6943798</v>
+        <v>6943946</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3311,6 +3306,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3340,7 +3340,7 @@
         <v>126020148</v>
       </c>
       <c r="B28" t="n">
-        <v>92510</v>
+        <v>92518</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3543,6 +3543,399 @@
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>126032975</v>
+      </c>
+      <c r="B30" t="n">
+        <v>78727</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Bodvikberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>549046</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6943812</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>126057406</v>
+      </c>
+      <c r="B31" t="n">
+        <v>92518</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Grössjöbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>549039</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6943833</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>13 exemplar</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>126023058</v>
+      </c>
+      <c r="B32" t="n">
+        <v>78727</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Bodvikberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>549141</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6943883</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>126023569</v>
+      </c>
+      <c r="B33" t="n">
+        <v>78727</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Bodvikberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>549060</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6943945</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24054-2025 artfynd.xlsx
+++ b/artfynd/A 24054-2025 artfynd.xlsx
@@ -675,37 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126022261</v>
+        <v>126020940</v>
       </c>
       <c r="B2" t="n">
-        <v>98334</v>
+        <v>92518</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549227</v>
+        <v>549196</v>
       </c>
       <c r="R2" t="n">
-        <v>6943821</v>
+        <v>6943799</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,37 +776,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126022283</v>
+        <v>126019996</v>
       </c>
       <c r="B3" t="n">
-        <v>98334</v>
+        <v>57651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -815,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549248</v>
+        <v>549046</v>
       </c>
       <c r="R3" t="n">
-        <v>6943846</v>
+        <v>6943812</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,6 +852,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,37 +883,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126020940</v>
+        <v>126022261</v>
       </c>
       <c r="B4" t="n">
-        <v>92518</v>
+        <v>98334</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>70</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -916,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549196</v>
+        <v>549227</v>
       </c>
       <c r="R4" t="n">
-        <v>6943799</v>
+        <v>6943821</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,38 +984,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126019996</v>
+        <v>126022283</v>
       </c>
       <c r="B5" t="n">
-        <v>57651</v>
+        <v>98334</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1018,10 +1023,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>549046</v>
+        <v>549248</v>
       </c>
       <c r="R5" t="n">
-        <v>6943812</v>
+        <v>6943846</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1054,11 +1059,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -3124,37 +3124,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126023135</v>
+        <v>126023512</v>
       </c>
       <c r="B26" t="n">
-        <v>92518</v>
+        <v>57651</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3163,10 +3164,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>549141</v>
+        <v>549050</v>
       </c>
       <c r="R26" t="n">
-        <v>6943883</v>
+        <v>6943946</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3203,7 +3204,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Äldre exemplar</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3230,38 +3231,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126023512</v>
+        <v>126023135</v>
       </c>
       <c r="B27" t="n">
-        <v>57651</v>
+        <v>92518</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3270,10 +3270,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>549050</v>
+        <v>549141</v>
       </c>
       <c r="R27" t="n">
-        <v>6943946</v>
+        <v>6943883</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 24054-2025 artfynd.xlsx
+++ b/artfynd/A 24054-2025 artfynd.xlsx
@@ -675,37 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126020940</v>
+        <v>126019996</v>
       </c>
       <c r="B2" t="n">
-        <v>92518</v>
+        <v>57651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>12</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549196</v>
+        <v>549046</v>
       </c>
       <c r="R2" t="n">
-        <v>6943799</v>
+        <v>6943812</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,38 +782,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126019996</v>
+        <v>126020940</v>
       </c>
       <c r="B3" t="n">
-        <v>57651</v>
+        <v>92522</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -816,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549046</v>
+        <v>549196</v>
       </c>
       <c r="R3" t="n">
-        <v>6943812</v>
+        <v>6943799</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,11 +857,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126022261</v>
+        <v>126022283</v>
       </c>
       <c r="B4" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549227</v>
+        <v>549248</v>
       </c>
       <c r="R4" t="n">
-        <v>6943821</v>
+        <v>6943846</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,10 +984,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126022283</v>
+        <v>126022261</v>
       </c>
       <c r="B5" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>70</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>549248</v>
+        <v>549227</v>
       </c>
       <c r="R5" t="n">
-        <v>6943846</v>
+        <v>6943821</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1088,7 @@
         <v>126022879</v>
       </c>
       <c r="B6" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>126020624</v>
       </c>
       <c r="B7" t="n">
-        <v>91193</v>
+        <v>91197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>126020676</v>
       </c>
       <c r="B8" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>126023583</v>
       </c>
       <c r="B9" t="n">
-        <v>97212</v>
+        <v>97216</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>126020477</v>
       </c>
       <c r="B10" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>126021032</v>
       </c>
       <c r="B11" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>126022352</v>
       </c>
       <c r="B12" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>126020410</v>
       </c>
       <c r="B13" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1910,42 +1910,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126021074</v>
+        <v>126023708</v>
       </c>
       <c r="B14" t="n">
-        <v>92518</v>
+        <v>98338</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1954,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>549255</v>
+        <v>549056</v>
       </c>
       <c r="R14" t="n">
-        <v>6943783</v>
+        <v>6943960</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1990,11 +1985,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2021,37 +2011,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126023708</v>
+        <v>126021074</v>
       </c>
       <c r="B15" t="n">
-        <v>98334</v>
+        <v>92522</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2060,10 +2055,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>549056</v>
+        <v>549255</v>
       </c>
       <c r="R15" t="n">
-        <v>6943960</v>
+        <v>6943783</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2096,6 +2091,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2229,37 +2229,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126022598</v>
+        <v>126022148</v>
       </c>
       <c r="B17" t="n">
-        <v>98334</v>
+        <v>58020</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>60</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2268,10 +2269,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>549225</v>
+        <v>549228</v>
       </c>
       <c r="R17" t="n">
-        <v>6943798</v>
+        <v>6943849</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2330,38 +2331,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126022148</v>
+        <v>126022598</v>
       </c>
       <c r="B18" t="n">
-        <v>58020</v>
+        <v>98338</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>60</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2370,10 +2370,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>549228</v>
+        <v>549225</v>
       </c>
       <c r="R18" t="n">
-        <v>6943849</v>
+        <v>6943798</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2432,45 +2432,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126020038</v>
+        <v>126020211</v>
       </c>
       <c r="B19" t="n">
-        <v>78968</v>
+        <v>56843</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>549039</v>
+        <v>549046</v>
       </c>
       <c r="R19" t="n">
-        <v>6943827</v>
+        <v>6943812</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2529,50 +2534,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126020211</v>
+        <v>126020038</v>
       </c>
       <c r="B20" t="n">
-        <v>56843</v>
+        <v>78972</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>549046</v>
+        <v>549039</v>
       </c>
       <c r="R20" t="n">
-        <v>6943812</v>
+        <v>6943827</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2631,45 +2631,49 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126022835</v>
+        <v>126022476</v>
       </c>
       <c r="B21" t="n">
-        <v>78968</v>
+        <v>98338</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>549178</v>
+        <v>549241</v>
       </c>
       <c r="R21" t="n">
-        <v>6943858</v>
+        <v>6943819</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2728,49 +2732,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126022476</v>
+        <v>126022835</v>
       </c>
       <c r="B22" t="n">
-        <v>98334</v>
+        <v>78972</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>549241</v>
+        <v>549178</v>
       </c>
       <c r="R22" t="n">
-        <v>6943819</v>
+        <v>6943858</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2832,7 +2832,7 @@
         <v>126020909</v>
       </c>
       <c r="B23" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>126023779</v>
       </c>
       <c r="B24" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3027,45 +3027,49 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126021627</v>
+        <v>126023135</v>
       </c>
       <c r="B25" t="n">
-        <v>78968</v>
+        <v>92522</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>549225</v>
+        <v>549141</v>
       </c>
       <c r="R25" t="n">
-        <v>6943798</v>
+        <v>6943883</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3098,6 +3102,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3124,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126023512</v>
+        <v>126021627</v>
       </c>
       <c r="B26" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3135,39 +3144,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>549050</v>
+        <v>549225</v>
       </c>
       <c r="R26" t="n">
-        <v>6943946</v>
+        <v>6943798</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3200,11 +3204,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3231,37 +3230,38 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126023135</v>
+        <v>126023512</v>
       </c>
       <c r="B27" t="n">
-        <v>92518</v>
+        <v>57651</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3270,10 +3270,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>549141</v>
+        <v>549050</v>
       </c>
       <c r="R27" t="n">
-        <v>6943883</v>
+        <v>6943946</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Äldre exemplar</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3340,7 +3340,7 @@
         <v>126020148</v>
       </c>
       <c r="B28" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         <v>126022593</v>
       </c>
       <c r="B29" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>126032975</v>
       </c>
       <c r="B30" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>126057406</v>
       </c>
       <c r="B31" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>126023058</v>
       </c>
       <c r="B32" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>126023569</v>
       </c>
       <c r="B33" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 24054-2025 artfynd.xlsx
+++ b/artfynd/A 24054-2025 artfynd.xlsx
@@ -1910,37 +1910,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126023708</v>
+        <v>126021074</v>
       </c>
       <c r="B14" t="n">
-        <v>98338</v>
+        <v>92522</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1949,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>549056</v>
+        <v>549255</v>
       </c>
       <c r="R14" t="n">
-        <v>6943960</v>
+        <v>6943783</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1985,6 +1990,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2011,42 +2021,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126021074</v>
+        <v>126023708</v>
       </c>
       <c r="B15" t="n">
-        <v>92522</v>
+        <v>98338</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2055,10 +2060,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>549255</v>
+        <v>549056</v>
       </c>
       <c r="R15" t="n">
-        <v>6943783</v>
+        <v>6943960</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2091,11 +2096,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2122,38 +2122,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126020126</v>
+        <v>126022598</v>
       </c>
       <c r="B16" t="n">
-        <v>57651</v>
+        <v>98338</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>60</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2162,10 +2161,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>549055</v>
+        <v>549225</v>
       </c>
       <c r="R16" t="n">
-        <v>6943810</v>
+        <v>6943798</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2198,11 +2197,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2229,27 +2223,27 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126022148</v>
+        <v>126020126</v>
       </c>
       <c r="B17" t="n">
-        <v>58020</v>
+        <v>57651</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2260,7 +2254,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2269,10 +2263,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>549228</v>
+        <v>549055</v>
       </c>
       <c r="R17" t="n">
-        <v>6943849</v>
+        <v>6943810</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2305,6 +2299,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2331,37 +2330,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126022598</v>
+        <v>126022148</v>
       </c>
       <c r="B18" t="n">
-        <v>98338</v>
+        <v>58020</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>60</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2370,10 +2370,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>549225</v>
+        <v>549228</v>
       </c>
       <c r="R18" t="n">
-        <v>6943798</v>
+        <v>6943849</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 24054-2025 artfynd.xlsx
+++ b/artfynd/A 24054-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126019996</v>
+        <v>126019990</v>
       </c>
       <c r="B2" t="n">
         <v>57651</v>
@@ -886,7 +886,7 @@
         <v>126022283</v>
       </c>
       <c r="B4" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>126022261</v>
       </c>
       <c r="B5" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1186,10 +1186,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126020624</v>
+        <v>126020676</v>
       </c>
       <c r="B7" t="n">
-        <v>91197</v>
+        <v>92522</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1197,34 +1197,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>549065</v>
+        <v>549093</v>
       </c>
       <c r="R7" t="n">
-        <v>6943839</v>
+        <v>6943852</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1283,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126020676</v>
+        <v>126020624</v>
       </c>
       <c r="B8" t="n">
-        <v>92522</v>
+        <v>91197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1294,38 +1298,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>549093</v>
+        <v>549065</v>
       </c>
       <c r="R8" t="n">
-        <v>6943852</v>
+        <v>6943839</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
         <v>126023583</v>
       </c>
       <c r="B9" t="n">
-        <v>97216</v>
+        <v>97217</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>126022352</v>
       </c>
       <c r="B12" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1910,42 +1910,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126021074</v>
+        <v>126023708</v>
       </c>
       <c r="B14" t="n">
-        <v>92522</v>
+        <v>98339</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1954,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>549255</v>
+        <v>549056</v>
       </c>
       <c r="R14" t="n">
-        <v>6943783</v>
+        <v>6943960</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1990,11 +1985,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2021,37 +2011,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126023708</v>
+        <v>126021074</v>
       </c>
       <c r="B15" t="n">
-        <v>98338</v>
+        <v>92522</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2060,10 +2055,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>549056</v>
+        <v>549255</v>
       </c>
       <c r="R15" t="n">
-        <v>6943960</v>
+        <v>6943783</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2096,6 +2091,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2125,7 +2125,7 @@
         <v>126022598</v>
       </c>
       <c r="B16" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2223,27 +2223,27 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126020126</v>
+        <v>126022148</v>
       </c>
       <c r="B17" t="n">
-        <v>57651</v>
+        <v>58020</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2254,7 +2254,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2263,10 +2263,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>549055</v>
+        <v>549228</v>
       </c>
       <c r="R17" t="n">
-        <v>6943810</v>
+        <v>6943849</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2299,11 +2299,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2330,27 +2325,27 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126022148</v>
+        <v>126020126</v>
       </c>
       <c r="B18" t="n">
-        <v>58020</v>
+        <v>57651</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2361,7 +2356,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2370,10 +2365,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>549228</v>
+        <v>549055</v>
       </c>
       <c r="R18" t="n">
-        <v>6943849</v>
+        <v>6943810</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2406,6 +2401,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2432,50 +2432,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126020211</v>
+        <v>126020038</v>
       </c>
       <c r="B19" t="n">
-        <v>56843</v>
+        <v>78972</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>549046</v>
+        <v>549039</v>
       </c>
       <c r="R19" t="n">
-        <v>6943812</v>
+        <v>6943827</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2534,45 +2529,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126020038</v>
+        <v>126020211</v>
       </c>
       <c r="B20" t="n">
-        <v>78972</v>
+        <v>56843</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>549039</v>
+        <v>549046</v>
       </c>
       <c r="R20" t="n">
-        <v>6943827</v>
+        <v>6943812</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2631,49 +2631,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126022476</v>
+        <v>126022835</v>
       </c>
       <c r="B21" t="n">
-        <v>98338</v>
+        <v>78972</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>549241</v>
+        <v>549178</v>
       </c>
       <c r="R21" t="n">
-        <v>6943819</v>
+        <v>6943858</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2732,45 +2728,49 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126022835</v>
+        <v>126022476</v>
       </c>
       <c r="B22" t="n">
-        <v>78972</v>
+        <v>98339</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>549178</v>
+        <v>549241</v>
       </c>
       <c r="R22" t="n">
-        <v>6943858</v>
+        <v>6943819</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2929,7 +2929,7 @@
         <v>126023779</v>
       </c>
       <c r="B24" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 24054-2025 artfynd.xlsx
+++ b/artfynd/A 24054-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126019990</v>
+        <v>126019996</v>
       </c>
       <c r="B2" t="n">
         <v>57651</v>
@@ -1384,10 +1384,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126023583</v>
+        <v>126020477</v>
       </c>
       <c r="B9" t="n">
-        <v>97217</v>
+        <v>92522</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1395,34 +1395,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>549060</v>
+        <v>549094</v>
       </c>
       <c r="R9" t="n">
-        <v>6943945</v>
+        <v>6943793</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1455,6 +1459,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1481,10 +1490,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126020477</v>
+        <v>126023583</v>
       </c>
       <c r="B10" t="n">
-        <v>92522</v>
+        <v>97217</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1492,38 +1501,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>549094</v>
+        <v>549060</v>
       </c>
       <c r="R10" t="n">
-        <v>6943793</v>
+        <v>6943945</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1556,11 +1561,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 24054-2025 artfynd.xlsx
+++ b/artfynd/A 24054-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126019996</v>
       </c>
       <c r="B2" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126020940</v>
       </c>
       <c r="B3" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>126022283</v>
       </c>
       <c r="B4" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>126022261</v>
       </c>
       <c r="B5" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>126022879</v>
       </c>
       <c r="B6" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1186,10 +1186,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126020676</v>
+        <v>126020624</v>
       </c>
       <c r="B7" t="n">
-        <v>92522</v>
+        <v>91199</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1197,38 +1197,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>549093</v>
+        <v>549065</v>
       </c>
       <c r="R7" t="n">
-        <v>6943852</v>
+        <v>6943839</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1283,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126020624</v>
+        <v>126020676</v>
       </c>
       <c r="B8" t="n">
-        <v>91197</v>
+        <v>92524</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1298,34 +1294,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>549065</v>
+        <v>549093</v>
       </c>
       <c r="R8" t="n">
-        <v>6943839</v>
+        <v>6943852</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
         <v>126020477</v>
       </c>
       <c r="B9" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>126023583</v>
       </c>
       <c r="B10" t="n">
-        <v>97217</v>
+        <v>97219</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>126021032</v>
       </c>
       <c r="B11" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>126022352</v>
       </c>
       <c r="B12" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>126020410</v>
       </c>
       <c r="B13" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1910,37 +1910,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126023708</v>
+        <v>126021074</v>
       </c>
       <c r="B14" t="n">
-        <v>98339</v>
+        <v>92524</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1949,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>549056</v>
+        <v>549255</v>
       </c>
       <c r="R14" t="n">
-        <v>6943960</v>
+        <v>6943783</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1985,6 +1990,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2011,42 +2021,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126021074</v>
+        <v>126023708</v>
       </c>
       <c r="B15" t="n">
-        <v>92522</v>
+        <v>98341</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2055,10 +2060,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>549255</v>
+        <v>549056</v>
       </c>
       <c r="R15" t="n">
-        <v>6943783</v>
+        <v>6943960</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2091,11 +2096,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2122,37 +2122,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126022598</v>
+        <v>126020126</v>
       </c>
       <c r="B16" t="n">
-        <v>98339</v>
+        <v>57652</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>60</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2161,10 +2162,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>549225</v>
+        <v>549055</v>
       </c>
       <c r="R16" t="n">
-        <v>6943798</v>
+        <v>6943810</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2197,6 +2198,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2226,7 +2232,7 @@
         <v>126022148</v>
       </c>
       <c r="B17" t="n">
-        <v>58020</v>
+        <v>58021</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2325,38 +2331,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126020126</v>
+        <v>126022598</v>
       </c>
       <c r="B18" t="n">
-        <v>57651</v>
+        <v>98341</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>60</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2365,10 +2370,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>549055</v>
+        <v>549225</v>
       </c>
       <c r="R18" t="n">
-        <v>6943810</v>
+        <v>6943798</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2401,11 +2406,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2432,45 +2432,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126020038</v>
+        <v>126020211</v>
       </c>
       <c r="B19" t="n">
-        <v>78972</v>
+        <v>56844</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>549039</v>
+        <v>549046</v>
       </c>
       <c r="R19" t="n">
-        <v>6943827</v>
+        <v>6943812</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2529,50 +2534,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126020211</v>
+        <v>126020038</v>
       </c>
       <c r="B20" t="n">
-        <v>56843</v>
+        <v>78973</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>549046</v>
+        <v>549039</v>
       </c>
       <c r="R20" t="n">
-        <v>6943812</v>
+        <v>6943827</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2634,7 +2634,7 @@
         <v>126022835</v>
       </c>
       <c r="B21" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>126022476</v>
       </c>
       <c r="B22" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>126020909</v>
       </c>
       <c r="B23" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>126023779</v>
       </c>
       <c r="B24" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3027,37 +3027,38 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126023135</v>
+        <v>126023512</v>
       </c>
       <c r="B25" t="n">
-        <v>92522</v>
+        <v>57652</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3066,10 +3067,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>549141</v>
+        <v>549050</v>
       </c>
       <c r="R25" t="n">
-        <v>6943883</v>
+        <v>6943946</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3106,7 +3107,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Äldre exemplar</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3136,7 +3137,7 @@
         <v>126021627</v>
       </c>
       <c r="B26" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3230,38 +3231,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126023512</v>
+        <v>126023135</v>
       </c>
       <c r="B27" t="n">
-        <v>57651</v>
+        <v>92524</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3270,10 +3270,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>549050</v>
+        <v>549141</v>
       </c>
       <c r="R27" t="n">
-        <v>6943946</v>
+        <v>6943883</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3340,7 +3340,7 @@
         <v>126020148</v>
       </c>
       <c r="B28" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         <v>126022593</v>
       </c>
       <c r="B29" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>126032975</v>
       </c>
       <c r="B30" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>126057406</v>
       </c>
       <c r="B31" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>126023058</v>
       </c>
       <c r="B32" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>126023569</v>
       </c>
       <c r="B33" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 24054-2025 artfynd.xlsx
+++ b/artfynd/A 24054-2025 artfynd.xlsx
@@ -2122,38 +2122,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126020126</v>
+        <v>126022598</v>
       </c>
       <c r="B16" t="n">
-        <v>57652</v>
+        <v>98341</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>60</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2162,10 +2161,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>549055</v>
+        <v>549225</v>
       </c>
       <c r="R16" t="n">
-        <v>6943810</v>
+        <v>6943798</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2198,11 +2197,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2229,27 +2223,27 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126022148</v>
+        <v>126020126</v>
       </c>
       <c r="B17" t="n">
-        <v>58021</v>
+        <v>57652</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2260,7 +2254,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2269,10 +2263,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>549228</v>
+        <v>549055</v>
       </c>
       <c r="R17" t="n">
-        <v>6943849</v>
+        <v>6943810</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2305,6 +2299,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2331,37 +2330,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126022598</v>
+        <v>126022148</v>
       </c>
       <c r="B18" t="n">
-        <v>98341</v>
+        <v>58021</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>60</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2370,10 +2370,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>549225</v>
+        <v>549228</v>
       </c>
       <c r="R18" t="n">
-        <v>6943798</v>
+        <v>6943849</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -3027,10 +3027,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126023512</v>
+        <v>126021627</v>
       </c>
       <c r="B25" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3038,39 +3038,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>549050</v>
+        <v>549225</v>
       </c>
       <c r="R25" t="n">
-        <v>6943946</v>
+        <v>6943798</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3103,11 +3098,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3134,45 +3124,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126021627</v>
+        <v>126023135</v>
       </c>
       <c r="B26" t="n">
-        <v>78973</v>
+        <v>92524</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>549225</v>
+        <v>549141</v>
       </c>
       <c r="R26" t="n">
-        <v>6943798</v>
+        <v>6943883</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3205,6 +3199,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3231,37 +3230,38 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126023135</v>
+        <v>126023512</v>
       </c>
       <c r="B27" t="n">
-        <v>92524</v>
+        <v>57652</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3270,10 +3270,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>549141</v>
+        <v>549050</v>
       </c>
       <c r="R27" t="n">
-        <v>6943883</v>
+        <v>6943946</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Äldre exemplar</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 24054-2025 artfynd.xlsx
+++ b/artfynd/A 24054-2025 artfynd.xlsx
@@ -675,38 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126019996</v>
+        <v>126020940</v>
       </c>
       <c r="B2" t="n">
-        <v>57652</v>
+        <v>92526</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549046</v>
+        <v>549196</v>
       </c>
       <c r="R2" t="n">
-        <v>6943812</v>
+        <v>6943799</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +750,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,37 +776,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126020940</v>
+        <v>126019996</v>
       </c>
       <c r="B3" t="n">
-        <v>92524</v>
+        <v>57652</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>12</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -821,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549196</v>
+        <v>549046</v>
       </c>
       <c r="R3" t="n">
-        <v>6943799</v>
+        <v>6943812</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,6 +852,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,7 +886,7 @@
         <v>126022283</v>
       </c>
       <c r="B4" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>126022261</v>
       </c>
       <c r="B5" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>126022879</v>
       </c>
       <c r="B6" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>126020624</v>
       </c>
       <c r="B7" t="n">
-        <v>91199</v>
+        <v>91201</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>126020676</v>
       </c>
       <c r="B8" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>126020477</v>
       </c>
       <c r="B9" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>126023583</v>
       </c>
       <c r="B10" t="n">
-        <v>97219</v>
+        <v>97221</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>126021032</v>
       </c>
       <c r="B11" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>126022352</v>
       </c>
       <c r="B12" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>126020410</v>
       </c>
       <c r="B13" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>126021074</v>
       </c>
       <c r="B14" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>126023708</v>
       </c>
       <c r="B15" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>126022598</v>
       </c>
       <c r="B16" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2432,50 +2432,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126020211</v>
+        <v>126020038</v>
       </c>
       <c r="B19" t="n">
-        <v>56844</v>
+        <v>78973</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>549046</v>
+        <v>549039</v>
       </c>
       <c r="R19" t="n">
-        <v>6943812</v>
+        <v>6943827</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2534,45 +2529,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126020038</v>
+        <v>126020211</v>
       </c>
       <c r="B20" t="n">
-        <v>78973</v>
+        <v>56844</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>549039</v>
+        <v>549046</v>
       </c>
       <c r="R20" t="n">
-        <v>6943827</v>
+        <v>6943812</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2731,7 +2731,7 @@
         <v>126022476</v>
       </c>
       <c r="B22" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>126023779</v>
       </c>
       <c r="B24" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3027,10 +3027,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126021627</v>
+        <v>126023512</v>
       </c>
       <c r="B25" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3038,34 +3038,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>549225</v>
+        <v>549050</v>
       </c>
       <c r="R25" t="n">
-        <v>6943798</v>
+        <v>6943946</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3098,6 +3103,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3127,7 +3137,7 @@
         <v>126023135</v>
       </c>
       <c r="B26" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3230,10 +3240,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126023512</v>
+        <v>126021627</v>
       </c>
       <c r="B27" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3241,39 +3251,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>549050</v>
+        <v>549225</v>
       </c>
       <c r="R27" t="n">
-        <v>6943946</v>
+        <v>6943798</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3306,11 +3311,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3340,7 +3340,7 @@
         <v>126020148</v>
       </c>
       <c r="B28" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>126057406</v>
       </c>
       <c r="B31" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 24054-2025 artfynd.xlsx
+++ b/artfynd/A 24054-2025 artfynd.xlsx
@@ -675,37 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126020940</v>
+        <v>126019990</v>
       </c>
       <c r="B2" t="n">
-        <v>92526</v>
+        <v>57652</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>12</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549196</v>
+        <v>549046</v>
       </c>
       <c r="R2" t="n">
-        <v>6943799</v>
+        <v>6943812</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,38 +782,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126019996</v>
+        <v>126020940</v>
       </c>
       <c r="B3" t="n">
-        <v>57652</v>
+        <v>92526</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -816,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549046</v>
+        <v>549196</v>
       </c>
       <c r="R3" t="n">
-        <v>6943812</v>
+        <v>6943799</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,11 +857,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 24054-2025 artfynd.xlsx
+++ b/artfynd/A 24054-2025 artfynd.xlsx
@@ -675,38 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126019990</v>
+        <v>126020940</v>
       </c>
       <c r="B2" t="n">
-        <v>57652</v>
+        <v>92528</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549046</v>
+        <v>549196</v>
       </c>
       <c r="R2" t="n">
-        <v>6943812</v>
+        <v>6943799</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +750,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,37 +776,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126020940</v>
+        <v>126019996</v>
       </c>
       <c r="B3" t="n">
-        <v>92526</v>
+        <v>57652</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>12</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -821,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549196</v>
+        <v>549046</v>
       </c>
       <c r="R3" t="n">
-        <v>6943799</v>
+        <v>6943812</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,6 +852,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126022283</v>
+        <v>126022261</v>
       </c>
       <c r="B4" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>70</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549248</v>
+        <v>549227</v>
       </c>
       <c r="R4" t="n">
-        <v>6943846</v>
+        <v>6943821</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,10 +984,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126022261</v>
+        <v>126022283</v>
       </c>
       <c r="B5" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>549227</v>
+        <v>549248</v>
       </c>
       <c r="R5" t="n">
-        <v>6943821</v>
+        <v>6943846</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1088,7 @@
         <v>126022879</v>
       </c>
       <c r="B6" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>126020624</v>
       </c>
       <c r="B7" t="n">
-        <v>91201</v>
+        <v>91203</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>126020676</v>
       </c>
       <c r="B8" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>126020477</v>
       </c>
       <c r="B9" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>126023583</v>
       </c>
       <c r="B10" t="n">
-        <v>97221</v>
+        <v>97223</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>126021032</v>
       </c>
       <c r="B11" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>126022352</v>
       </c>
       <c r="B12" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>126020410</v>
       </c>
       <c r="B13" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1910,42 +1910,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126021074</v>
+        <v>126023708</v>
       </c>
       <c r="B14" t="n">
-        <v>92526</v>
+        <v>98345</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1954,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>549255</v>
+        <v>549056</v>
       </c>
       <c r="R14" t="n">
-        <v>6943783</v>
+        <v>6943960</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1990,11 +1985,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2021,37 +2011,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126023708</v>
+        <v>126021074</v>
       </c>
       <c r="B15" t="n">
-        <v>98343</v>
+        <v>92528</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2060,10 +2055,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>549056</v>
+        <v>549255</v>
       </c>
       <c r="R15" t="n">
-        <v>6943960</v>
+        <v>6943783</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2096,6 +2091,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2122,37 +2122,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126022598</v>
+        <v>126022148</v>
       </c>
       <c r="B16" t="n">
-        <v>98343</v>
+        <v>58021</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>60</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2161,10 +2162,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>549225</v>
+        <v>549228</v>
       </c>
       <c r="R16" t="n">
-        <v>6943798</v>
+        <v>6943849</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2223,38 +2224,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126020126</v>
+        <v>126022598</v>
       </c>
       <c r="B17" t="n">
-        <v>57652</v>
+        <v>98345</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>60</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2263,10 +2263,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>549055</v>
+        <v>549225</v>
       </c>
       <c r="R17" t="n">
-        <v>6943810</v>
+        <v>6943798</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2299,11 +2299,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2330,27 +2325,27 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126022148</v>
+        <v>126020126</v>
       </c>
       <c r="B18" t="n">
-        <v>58021</v>
+        <v>57652</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2361,7 +2356,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2370,10 +2365,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>549228</v>
+        <v>549055</v>
       </c>
       <c r="R18" t="n">
-        <v>6943849</v>
+        <v>6943810</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2406,6 +2401,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2631,45 +2631,49 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126022835</v>
+        <v>126022476</v>
       </c>
       <c r="B21" t="n">
-        <v>78973</v>
+        <v>98345</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>549178</v>
+        <v>549241</v>
       </c>
       <c r="R21" t="n">
-        <v>6943858</v>
+        <v>6943819</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2728,49 +2732,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126022476</v>
+        <v>126022835</v>
       </c>
       <c r="B22" t="n">
-        <v>98343</v>
+        <v>78973</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>549241</v>
+        <v>549178</v>
       </c>
       <c r="R22" t="n">
-        <v>6943819</v>
+        <v>6943858</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2929,7 +2929,7 @@
         <v>126023779</v>
       </c>
       <c r="B24" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3134,49 +3134,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126023135</v>
+        <v>126021627</v>
       </c>
       <c r="B26" t="n">
-        <v>92526</v>
+        <v>78973</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>549141</v>
+        <v>549225</v>
       </c>
       <c r="R26" t="n">
-        <v>6943883</v>
+        <v>6943798</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3209,11 +3205,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3240,45 +3231,49 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126021627</v>
+        <v>126023135</v>
       </c>
       <c r="B27" t="n">
-        <v>78973</v>
+        <v>92528</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>549225</v>
+        <v>549141</v>
       </c>
       <c r="R27" t="n">
-        <v>6943798</v>
+        <v>6943883</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3311,6 +3306,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3340,7 +3340,7 @@
         <v>126020148</v>
       </c>
       <c r="B28" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>126057406</v>
       </c>
       <c r="B31" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 24054-2025 artfynd.xlsx
+++ b/artfynd/A 24054-2025 artfynd.xlsx
@@ -1910,37 +1910,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126023708</v>
+        <v>126021074</v>
       </c>
       <c r="B14" t="n">
-        <v>98345</v>
+        <v>92528</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1949,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>549056</v>
+        <v>549255</v>
       </c>
       <c r="R14" t="n">
-        <v>6943960</v>
+        <v>6943783</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1985,6 +1990,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2011,42 +2021,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126021074</v>
+        <v>126023708</v>
       </c>
       <c r="B15" t="n">
-        <v>92528</v>
+        <v>98345</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2055,10 +2060,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>549255</v>
+        <v>549056</v>
       </c>
       <c r="R15" t="n">
-        <v>6943783</v>
+        <v>6943960</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2091,11 +2096,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2122,27 +2122,27 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126022148</v>
+        <v>126020126</v>
       </c>
       <c r="B16" t="n">
-        <v>58021</v>
+        <v>57652</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2153,7 +2153,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>549228</v>
+        <v>549055</v>
       </c>
       <c r="R16" t="n">
-        <v>6943849</v>
+        <v>6943810</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2198,6 +2198,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2224,37 +2229,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126022598</v>
+        <v>126022148</v>
       </c>
       <c r="B17" t="n">
-        <v>98345</v>
+        <v>58021</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>60</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2263,10 +2269,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>549225</v>
+        <v>549228</v>
       </c>
       <c r="R17" t="n">
-        <v>6943798</v>
+        <v>6943849</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2325,38 +2331,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126020126</v>
+        <v>126022598</v>
       </c>
       <c r="B18" t="n">
-        <v>57652</v>
+        <v>98345</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>60</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2365,10 +2370,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>549055</v>
+        <v>549225</v>
       </c>
       <c r="R18" t="n">
-        <v>6943810</v>
+        <v>6943798</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2401,11 +2406,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 24054-2025 artfynd.xlsx
+++ b/artfynd/A 24054-2025 artfynd.xlsx
@@ -675,37 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126020940</v>
+        <v>126022261</v>
       </c>
       <c r="B2" t="n">
-        <v>92528</v>
+        <v>98349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>70</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549196</v>
+        <v>549227</v>
       </c>
       <c r="R2" t="n">
-        <v>6943799</v>
+        <v>6943821</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,38 +776,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126019996</v>
+        <v>126020940</v>
       </c>
       <c r="B3" t="n">
-        <v>57652</v>
+        <v>92532</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -816,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549046</v>
+        <v>549196</v>
       </c>
       <c r="R3" t="n">
-        <v>6943812</v>
+        <v>6943799</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,11 +851,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,37 +877,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126022261</v>
+        <v>126019996</v>
       </c>
       <c r="B4" t="n">
-        <v>98345</v>
+        <v>57656</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>70</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -922,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549227</v>
+        <v>549046</v>
       </c>
       <c r="R4" t="n">
-        <v>6943821</v>
+        <v>6943812</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -958,6 +953,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -987,7 +987,7 @@
         <v>126022283</v>
       </c>
       <c r="B5" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>126022879</v>
       </c>
       <c r="B6" t="n">
-        <v>92528</v>
+        <v>92532</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>126020624</v>
       </c>
       <c r="B7" t="n">
-        <v>91203</v>
+        <v>91207</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>126020676</v>
       </c>
       <c r="B8" t="n">
-        <v>92528</v>
+        <v>92532</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>126020477</v>
       </c>
       <c r="B9" t="n">
-        <v>92528</v>
+        <v>92532</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>126023583</v>
       </c>
       <c r="B10" t="n">
-        <v>97223</v>
+        <v>97227</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,42 +1587,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126021032</v>
+        <v>126022352</v>
       </c>
       <c r="B11" t="n">
-        <v>92528</v>
+        <v>98349</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1631,10 +1626,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>549225</v>
+        <v>549222</v>
       </c>
       <c r="R11" t="n">
-        <v>6943798</v>
+        <v>6943831</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1667,11 +1662,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1698,37 +1688,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126022352</v>
+        <v>126021032</v>
       </c>
       <c r="B12" t="n">
-        <v>98345</v>
+        <v>92532</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1737,10 +1732,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>549222</v>
+        <v>549225</v>
       </c>
       <c r="R12" t="n">
-        <v>6943831</v>
+        <v>6943798</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1773,6 +1768,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1802,7 +1802,7 @@
         <v>126020410</v>
       </c>
       <c r="B13" t="n">
-        <v>92528</v>
+        <v>92532</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>126021074</v>
       </c>
       <c r="B14" t="n">
-        <v>92528</v>
+        <v>92532</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>126023708</v>
       </c>
       <c r="B15" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>126020126</v>
       </c>
       <c r="B16" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2229,38 +2229,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126022148</v>
+        <v>126022598</v>
       </c>
       <c r="B17" t="n">
-        <v>58021</v>
+        <v>98349</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>60</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2269,10 +2268,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>549228</v>
+        <v>549225</v>
       </c>
       <c r="R17" t="n">
-        <v>6943849</v>
+        <v>6943798</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2331,37 +2330,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126022598</v>
+        <v>126022148</v>
       </c>
       <c r="B18" t="n">
-        <v>98345</v>
+        <v>58025</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>60</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2370,10 +2370,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>549225</v>
+        <v>549228</v>
       </c>
       <c r="R18" t="n">
-        <v>6943798</v>
+        <v>6943849</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2435,7 +2435,7 @@
         <v>126020038</v>
       </c>
       <c r="B19" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>126020211</v>
       </c>
       <c r="B20" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2631,49 +2631,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126022476</v>
+        <v>126022835</v>
       </c>
       <c r="B21" t="n">
-        <v>98345</v>
+        <v>78977</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>549241</v>
+        <v>549178</v>
       </c>
       <c r="R21" t="n">
-        <v>6943819</v>
+        <v>6943858</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2732,45 +2728,49 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126022835</v>
+        <v>126022476</v>
       </c>
       <c r="B22" t="n">
-        <v>78973</v>
+        <v>98349</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>549178</v>
+        <v>549241</v>
       </c>
       <c r="R22" t="n">
-        <v>6943858</v>
+        <v>6943819</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2832,7 +2832,7 @@
         <v>126020909</v>
       </c>
       <c r="B23" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>126023779</v>
       </c>
       <c r="B24" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3027,10 +3027,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126023512</v>
+        <v>126021627</v>
       </c>
       <c r="B25" t="n">
-        <v>57652</v>
+        <v>78977</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3038,39 +3038,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>549050</v>
+        <v>549225</v>
       </c>
       <c r="R25" t="n">
-        <v>6943946</v>
+        <v>6943798</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3103,11 +3098,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3134,45 +3124,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126021627</v>
+        <v>126023135</v>
       </c>
       <c r="B26" t="n">
-        <v>78973</v>
+        <v>92532</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>549225</v>
+        <v>549141</v>
       </c>
       <c r="R26" t="n">
-        <v>6943798</v>
+        <v>6943883</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3205,6 +3199,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3231,37 +3230,38 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126023135</v>
+        <v>126023512</v>
       </c>
       <c r="B27" t="n">
-        <v>92528</v>
+        <v>57656</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3270,10 +3270,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>549141</v>
+        <v>549050</v>
       </c>
       <c r="R27" t="n">
-        <v>6943883</v>
+        <v>6943946</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Äldre exemplar</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3340,7 +3340,7 @@
         <v>126020148</v>
       </c>
       <c r="B28" t="n">
-        <v>92528</v>
+        <v>92532</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         <v>126022593</v>
       </c>
       <c r="B29" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>126032975</v>
       </c>
       <c r="B30" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>126057406</v>
       </c>
       <c r="B31" t="n">
-        <v>92528</v>
+        <v>92532</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>126023058</v>
       </c>
       <c r="B32" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>126023569</v>
       </c>
       <c r="B33" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 24054-2025 artfynd.xlsx
+++ b/artfynd/A 24054-2025 artfynd.xlsx
@@ -776,37 +776,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126020940</v>
+        <v>126022283</v>
       </c>
       <c r="B3" t="n">
-        <v>92532</v>
+        <v>98349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549196</v>
+        <v>549248</v>
       </c>
       <c r="R3" t="n">
-        <v>6943799</v>
+        <v>6943846</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -984,37 +984,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126022283</v>
+        <v>126020940</v>
       </c>
       <c r="B5" t="n">
-        <v>98349</v>
+        <v>92532</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>549248</v>
+        <v>549196</v>
       </c>
       <c r="R5" t="n">
-        <v>6943846</v>
+        <v>6943799</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -2631,45 +2631,49 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126022835</v>
+        <v>126022476</v>
       </c>
       <c r="B21" t="n">
-        <v>78977</v>
+        <v>98349</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>549178</v>
+        <v>549241</v>
       </c>
       <c r="R21" t="n">
-        <v>6943858</v>
+        <v>6943819</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2728,49 +2732,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126022476</v>
+        <v>126022835</v>
       </c>
       <c r="B22" t="n">
-        <v>98349</v>
+        <v>78977</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>549241</v>
+        <v>549178</v>
       </c>
       <c r="R22" t="n">
-        <v>6943819</v>
+        <v>6943858</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 24054-2025 artfynd.xlsx
+++ b/artfynd/A 24054-2025 artfynd.xlsx
@@ -675,37 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126022261</v>
+        <v>126019996</v>
       </c>
       <c r="B2" t="n">
-        <v>98349</v>
+        <v>57656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>70</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549227</v>
+        <v>549046</v>
       </c>
       <c r="R2" t="n">
-        <v>6943821</v>
+        <v>6943812</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,37 +782,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126022283</v>
+        <v>126020940</v>
       </c>
       <c r="B3" t="n">
-        <v>98349</v>
+        <v>92532</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -815,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549248</v>
+        <v>549196</v>
       </c>
       <c r="R3" t="n">
-        <v>6943846</v>
+        <v>6943799</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,38 +883,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126019996</v>
+        <v>126022283</v>
       </c>
       <c r="B4" t="n">
-        <v>57656</v>
+        <v>98352</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -917,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549046</v>
+        <v>549248</v>
       </c>
       <c r="R4" t="n">
-        <v>6943812</v>
+        <v>6943846</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -953,11 +958,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,37 +984,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126020940</v>
+        <v>126022261</v>
       </c>
       <c r="B5" t="n">
-        <v>92532</v>
+        <v>98352</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>70</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>549196</v>
+        <v>549227</v>
       </c>
       <c r="R5" t="n">
-        <v>6943799</v>
+        <v>6943821</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1186,10 +1186,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126020624</v>
+        <v>126020676</v>
       </c>
       <c r="B7" t="n">
-        <v>91207</v>
+        <v>92532</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1197,34 +1197,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>549065</v>
+        <v>549093</v>
       </c>
       <c r="R7" t="n">
-        <v>6943839</v>
+        <v>6943852</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1283,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126020676</v>
+        <v>126020624</v>
       </c>
       <c r="B8" t="n">
-        <v>92532</v>
+        <v>91207</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1294,38 +1298,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>549093</v>
+        <v>549065</v>
       </c>
       <c r="R8" t="n">
-        <v>6943852</v>
+        <v>6943839</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1493,7 +1493,7 @@
         <v>126023583</v>
       </c>
       <c r="B10" t="n">
-        <v>97227</v>
+        <v>97230</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,37 +1587,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126022352</v>
+        <v>126021032</v>
       </c>
       <c r="B11" t="n">
-        <v>98349</v>
+        <v>92532</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1626,10 +1631,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>549222</v>
+        <v>549225</v>
       </c>
       <c r="R11" t="n">
-        <v>6943831</v>
+        <v>6943798</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1662,6 +1667,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1688,42 +1698,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126021032</v>
+        <v>126022352</v>
       </c>
       <c r="B12" t="n">
-        <v>92532</v>
+        <v>98352</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1732,10 +1737,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>549225</v>
+        <v>549222</v>
       </c>
       <c r="R12" t="n">
-        <v>6943798</v>
+        <v>6943831</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1768,11 +1773,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2024,7 +2024,7 @@
         <v>126023708</v>
       </c>
       <c r="B15" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2122,27 +2122,27 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126020126</v>
+        <v>126022148</v>
       </c>
       <c r="B16" t="n">
-        <v>57656</v>
+        <v>58025</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2153,7 +2153,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>549055</v>
+        <v>549228</v>
       </c>
       <c r="R16" t="n">
-        <v>6943810</v>
+        <v>6943849</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2198,11 +2198,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2232,7 +2227,7 @@
         <v>126022598</v>
       </c>
       <c r="B17" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2330,27 +2325,27 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126022148</v>
+        <v>126020126</v>
       </c>
       <c r="B18" t="n">
-        <v>58025</v>
+        <v>57656</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2361,7 +2356,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2370,10 +2365,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>549228</v>
+        <v>549055</v>
       </c>
       <c r="R18" t="n">
-        <v>6943849</v>
+        <v>6943810</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2406,6 +2401,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2432,45 +2432,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126020038</v>
+        <v>126020211</v>
       </c>
       <c r="B19" t="n">
-        <v>78977</v>
+        <v>56848</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>549039</v>
+        <v>549046</v>
       </c>
       <c r="R19" t="n">
-        <v>6943827</v>
+        <v>6943812</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2529,50 +2534,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126020211</v>
+        <v>126020038</v>
       </c>
       <c r="B20" t="n">
-        <v>56848</v>
+        <v>78977</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>549046</v>
+        <v>549039</v>
       </c>
       <c r="R20" t="n">
-        <v>6943812</v>
+        <v>6943827</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2631,49 +2631,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126022476</v>
+        <v>126022835</v>
       </c>
       <c r="B21" t="n">
-        <v>98349</v>
+        <v>78977</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>549241</v>
+        <v>549178</v>
       </c>
       <c r="R21" t="n">
-        <v>6943819</v>
+        <v>6943858</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2732,45 +2728,49 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126022835</v>
+        <v>126022476</v>
       </c>
       <c r="B22" t="n">
-        <v>78977</v>
+        <v>98352</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>549178</v>
+        <v>549241</v>
       </c>
       <c r="R22" t="n">
-        <v>6943858</v>
+        <v>6943819</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2929,7 +2929,7 @@
         <v>126023779</v>
       </c>
       <c r="B24" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3027,10 +3027,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126021627</v>
+        <v>126023512</v>
       </c>
       <c r="B25" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3038,34 +3038,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>549225</v>
+        <v>549050</v>
       </c>
       <c r="R25" t="n">
-        <v>6943798</v>
+        <v>6943946</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3098,6 +3103,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3230,10 +3240,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126023512</v>
+        <v>126021627</v>
       </c>
       <c r="B27" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3241,39 +3251,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>549050</v>
+        <v>549225</v>
       </c>
       <c r="R27" t="n">
-        <v>6943946</v>
+        <v>6943798</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3306,11 +3311,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 24054-2025 artfynd.xlsx
+++ b/artfynd/A 24054-2025 artfynd.xlsx
@@ -1186,10 +1186,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126020676</v>
+        <v>126020624</v>
       </c>
       <c r="B7" t="n">
-        <v>92532</v>
+        <v>91207</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1197,38 +1197,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>549093</v>
+        <v>549065</v>
       </c>
       <c r="R7" t="n">
-        <v>6943852</v>
+        <v>6943839</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1283,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126020624</v>
+        <v>126020676</v>
       </c>
       <c r="B8" t="n">
-        <v>91207</v>
+        <v>92532</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1298,34 +1294,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>549065</v>
+        <v>549093</v>
       </c>
       <c r="R8" t="n">
-        <v>6943839</v>
+        <v>6943852</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1587,42 +1587,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126021032</v>
+        <v>126022352</v>
       </c>
       <c r="B11" t="n">
-        <v>92532</v>
+        <v>98352</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1631,10 +1626,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>549225</v>
+        <v>549222</v>
       </c>
       <c r="R11" t="n">
-        <v>6943798</v>
+        <v>6943831</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1667,11 +1662,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1698,37 +1688,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126022352</v>
+        <v>126021032</v>
       </c>
       <c r="B12" t="n">
-        <v>98352</v>
+        <v>92532</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1737,10 +1732,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>549222</v>
+        <v>549225</v>
       </c>
       <c r="R12" t="n">
-        <v>6943831</v>
+        <v>6943798</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1773,6 +1768,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2122,27 +2122,27 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126022148</v>
+        <v>126020126</v>
       </c>
       <c r="B16" t="n">
-        <v>58025</v>
+        <v>57656</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2153,7 +2153,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>549228</v>
+        <v>549055</v>
       </c>
       <c r="R16" t="n">
-        <v>6943849</v>
+        <v>6943810</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2198,6 +2198,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2224,37 +2229,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126022598</v>
+        <v>126022148</v>
       </c>
       <c r="B17" t="n">
-        <v>98352</v>
+        <v>58025</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>60</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2263,10 +2269,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>549225</v>
+        <v>549228</v>
       </c>
       <c r="R17" t="n">
-        <v>6943798</v>
+        <v>6943849</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2325,38 +2331,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126020126</v>
+        <v>126022598</v>
       </c>
       <c r="B18" t="n">
-        <v>57656</v>
+        <v>98352</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>60</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2365,10 +2370,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>549055</v>
+        <v>549225</v>
       </c>
       <c r="R18" t="n">
-        <v>6943810</v>
+        <v>6943798</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2401,11 +2406,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3027,10 +3027,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126023512</v>
+        <v>126021627</v>
       </c>
       <c r="B25" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3038,39 +3038,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>549050</v>
+        <v>549225</v>
       </c>
       <c r="R25" t="n">
-        <v>6943946</v>
+        <v>6943798</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3103,11 +3098,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3134,37 +3124,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126023135</v>
+        <v>126023512</v>
       </c>
       <c r="B26" t="n">
-        <v>92532</v>
+        <v>57656</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3173,10 +3164,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>549141</v>
+        <v>549050</v>
       </c>
       <c r="R26" t="n">
-        <v>6943883</v>
+        <v>6943946</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3213,7 +3204,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Äldre exemplar</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3240,45 +3231,49 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126021627</v>
+        <v>126023135</v>
       </c>
       <c r="B27" t="n">
-        <v>78977</v>
+        <v>92532</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>549225</v>
+        <v>549141</v>
       </c>
       <c r="R27" t="n">
-        <v>6943798</v>
+        <v>6943883</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3311,6 +3306,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 24054-2025 artfynd.xlsx
+++ b/artfynd/A 24054-2025 artfynd.xlsx
@@ -675,38 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126019996</v>
+        <v>126020940</v>
       </c>
       <c r="B2" t="n">
-        <v>57656</v>
+        <v>92532</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549046</v>
+        <v>549196</v>
       </c>
       <c r="R2" t="n">
-        <v>6943812</v>
+        <v>6943799</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +750,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,37 +776,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126020940</v>
+        <v>126019996</v>
       </c>
       <c r="B3" t="n">
-        <v>92532</v>
+        <v>57656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>12</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -821,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549196</v>
+        <v>549046</v>
       </c>
       <c r="R3" t="n">
-        <v>6943799</v>
+        <v>6943812</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,6 +852,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1384,10 +1384,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126020477</v>
+        <v>126023583</v>
       </c>
       <c r="B9" t="n">
-        <v>92532</v>
+        <v>97230</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1395,38 +1395,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>549094</v>
+        <v>549060</v>
       </c>
       <c r="R9" t="n">
-        <v>6943793</v>
+        <v>6943945</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,11 +1455,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1490,10 +1481,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126023583</v>
+        <v>126020477</v>
       </c>
       <c r="B10" t="n">
-        <v>97230</v>
+        <v>92532</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1501,34 +1492,38 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>549060</v>
+        <v>549094</v>
       </c>
       <c r="R10" t="n">
-        <v>6943945</v>
+        <v>6943793</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1561,6 +1556,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1587,37 +1587,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126022352</v>
+        <v>126021032</v>
       </c>
       <c r="B11" t="n">
-        <v>98352</v>
+        <v>92532</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1626,10 +1631,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>549222</v>
+        <v>549225</v>
       </c>
       <c r="R11" t="n">
-        <v>6943831</v>
+        <v>6943798</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1662,6 +1667,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1688,42 +1698,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126021032</v>
+        <v>126022352</v>
       </c>
       <c r="B12" t="n">
-        <v>92532</v>
+        <v>98352</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1732,10 +1737,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>549225</v>
+        <v>549222</v>
       </c>
       <c r="R12" t="n">
-        <v>6943798</v>
+        <v>6943831</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1768,11 +1773,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2432,50 +2432,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126020211</v>
+        <v>126020038</v>
       </c>
       <c r="B19" t="n">
-        <v>56848</v>
+        <v>78977</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>549046</v>
+        <v>549039</v>
       </c>
       <c r="R19" t="n">
-        <v>6943812</v>
+        <v>6943827</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2534,45 +2529,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126020038</v>
+        <v>126020211</v>
       </c>
       <c r="B20" t="n">
-        <v>78977</v>
+        <v>56848</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>549039</v>
+        <v>549046</v>
       </c>
       <c r="R20" t="n">
-        <v>6943827</v>
+        <v>6943812</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3124,38 +3124,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126023512</v>
+        <v>126023135</v>
       </c>
       <c r="B26" t="n">
-        <v>57656</v>
+        <v>92532</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3164,10 +3163,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>549050</v>
+        <v>549141</v>
       </c>
       <c r="R26" t="n">
-        <v>6943946</v>
+        <v>6943883</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3204,7 +3203,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3231,37 +3230,38 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126023135</v>
+        <v>126023512</v>
       </c>
       <c r="B27" t="n">
-        <v>92532</v>
+        <v>57656</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3270,10 +3270,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>549141</v>
+        <v>549050</v>
       </c>
       <c r="R27" t="n">
-        <v>6943883</v>
+        <v>6943946</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Äldre exemplar</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 24054-2025 artfynd.xlsx
+++ b/artfynd/A 24054-2025 artfynd.xlsx
@@ -2432,45 +2432,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126020038</v>
+        <v>126020211</v>
       </c>
       <c r="B19" t="n">
-        <v>78977</v>
+        <v>56848</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>549039</v>
+        <v>549046</v>
       </c>
       <c r="R19" t="n">
-        <v>6943827</v>
+        <v>6943812</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2529,50 +2534,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126020211</v>
+        <v>126020038</v>
       </c>
       <c r="B20" t="n">
-        <v>56848</v>
+        <v>78977</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>549046</v>
+        <v>549039</v>
       </c>
       <c r="R20" t="n">
-        <v>6943812</v>
+        <v>6943827</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 24054-2025 artfynd.xlsx
+++ b/artfynd/A 24054-2025 artfynd.xlsx
@@ -675,37 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126020940</v>
+        <v>126019996</v>
       </c>
       <c r="B2" t="n">
-        <v>92532</v>
+        <v>57657</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>12</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549196</v>
+        <v>549046</v>
       </c>
       <c r="R2" t="n">
-        <v>6943799</v>
+        <v>6943812</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,38 +782,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126019996</v>
+        <v>126022261</v>
       </c>
       <c r="B3" t="n">
-        <v>57656</v>
+        <v>98361</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>70</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -816,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549046</v>
+        <v>549227</v>
       </c>
       <c r="R3" t="n">
-        <v>6943812</v>
+        <v>6943821</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,11 +857,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,7 +886,7 @@
         <v>126022283</v>
       </c>
       <c r="B4" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,37 +984,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126022261</v>
+        <v>126020940</v>
       </c>
       <c r="B5" t="n">
-        <v>98352</v>
+        <v>92535</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>549227</v>
+        <v>549196</v>
       </c>
       <c r="R5" t="n">
-        <v>6943821</v>
+        <v>6943799</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1088,7 @@
         <v>126022879</v>
       </c>
       <c r="B6" t="n">
-        <v>92532</v>
+        <v>92535</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>126020624</v>
       </c>
       <c r="B7" t="n">
-        <v>91207</v>
+        <v>91210</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>126020676</v>
       </c>
       <c r="B8" t="n">
-        <v>92532</v>
+        <v>92535</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>126023583</v>
       </c>
       <c r="B9" t="n">
-        <v>97230</v>
+        <v>97239</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>126020477</v>
       </c>
       <c r="B10" t="n">
-        <v>92532</v>
+        <v>92535</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>126021032</v>
       </c>
       <c r="B11" t="n">
-        <v>92532</v>
+        <v>92535</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>126022352</v>
       </c>
       <c r="B12" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>126020410</v>
       </c>
       <c r="B13" t="n">
-        <v>92532</v>
+        <v>92535</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>126021074</v>
       </c>
       <c r="B14" t="n">
-        <v>92532</v>
+        <v>92535</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>126023708</v>
       </c>
       <c r="B15" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2122,27 +2122,27 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126020126</v>
+        <v>126022148</v>
       </c>
       <c r="B16" t="n">
-        <v>57656</v>
+        <v>58027</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2153,7 +2153,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>549055</v>
+        <v>549228</v>
       </c>
       <c r="R16" t="n">
-        <v>6943810</v>
+        <v>6943849</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2198,11 +2198,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2229,38 +2224,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126022148</v>
+        <v>126022598</v>
       </c>
       <c r="B17" t="n">
-        <v>58025</v>
+        <v>98361</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>60</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2269,10 +2263,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>549228</v>
+        <v>549225</v>
       </c>
       <c r="R17" t="n">
-        <v>6943849</v>
+        <v>6943798</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2331,37 +2325,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126022598</v>
+        <v>126020126</v>
       </c>
       <c r="B18" t="n">
-        <v>98352</v>
+        <v>57657</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>60</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2370,10 +2365,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>549225</v>
+        <v>549055</v>
       </c>
       <c r="R18" t="n">
-        <v>6943798</v>
+        <v>6943810</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2406,6 +2401,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2432,50 +2432,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126020211</v>
+        <v>126020038</v>
       </c>
       <c r="B19" t="n">
-        <v>56848</v>
+        <v>78980</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>549046</v>
+        <v>549039</v>
       </c>
       <c r="R19" t="n">
-        <v>6943812</v>
+        <v>6943827</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2534,45 +2529,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126020038</v>
+        <v>126020211</v>
       </c>
       <c r="B20" t="n">
-        <v>78977</v>
+        <v>56849</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>549039</v>
+        <v>549046</v>
       </c>
       <c r="R20" t="n">
-        <v>6943827</v>
+        <v>6943812</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2634,7 +2634,7 @@
         <v>126022835</v>
       </c>
       <c r="B21" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>126022476</v>
       </c>
       <c r="B22" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>126020909</v>
       </c>
       <c r="B23" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>126023779</v>
       </c>
       <c r="B24" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>126021627</v>
       </c>
       <c r="B25" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
         <v>126023135</v>
       </c>
       <c r="B26" t="n">
-        <v>92532</v>
+        <v>92535</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>126023512</v>
       </c>
       <c r="B27" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>126020148</v>
       </c>
       <c r="B28" t="n">
-        <v>92532</v>
+        <v>92535</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         <v>126022593</v>
       </c>
       <c r="B29" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>126032975</v>
       </c>
       <c r="B30" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>126057406</v>
       </c>
       <c r="B31" t="n">
-        <v>92532</v>
+        <v>92535</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>126023058</v>
       </c>
       <c r="B32" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>126023569</v>
       </c>
       <c r="B33" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 24054-2025 artfynd.xlsx
+++ b/artfynd/A 24054-2025 artfynd.xlsx
@@ -675,38 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126019996</v>
+        <v>126020940</v>
       </c>
       <c r="B2" t="n">
-        <v>57657</v>
+        <v>92535</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549046</v>
+        <v>549196</v>
       </c>
       <c r="R2" t="n">
-        <v>6943812</v>
+        <v>6943799</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +750,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,37 +776,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126022261</v>
+        <v>126019996</v>
       </c>
       <c r="B3" t="n">
-        <v>98361</v>
+        <v>57657</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>70</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -821,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549227</v>
+        <v>549046</v>
       </c>
       <c r="R3" t="n">
-        <v>6943821</v>
+        <v>6943812</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,6 +852,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -984,37 +984,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126020940</v>
+        <v>126022261</v>
       </c>
       <c r="B5" t="n">
-        <v>92535</v>
+        <v>98361</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>70</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>549196</v>
+        <v>549227</v>
       </c>
       <c r="R5" t="n">
-        <v>6943799</v>
+        <v>6943821</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -2631,45 +2631,49 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126022835</v>
+        <v>126022476</v>
       </c>
       <c r="B21" t="n">
-        <v>78980</v>
+        <v>98361</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>549178</v>
+        <v>549241</v>
       </c>
       <c r="R21" t="n">
-        <v>6943858</v>
+        <v>6943819</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2728,49 +2732,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126022476</v>
+        <v>126022835</v>
       </c>
       <c r="B22" t="n">
-        <v>98361</v>
+        <v>78980</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>549241</v>
+        <v>549178</v>
       </c>
       <c r="R22" t="n">
-        <v>6943819</v>
+        <v>6943858</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 24054-2025 artfynd.xlsx
+++ b/artfynd/A 24054-2025 artfynd.xlsx
@@ -675,37 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126020940</v>
+        <v>126022283</v>
       </c>
       <c r="B2" t="n">
-        <v>92535</v>
+        <v>98361</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549196</v>
+        <v>549248</v>
       </c>
       <c r="R2" t="n">
-        <v>6943799</v>
+        <v>6943846</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,38 +776,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126019996</v>
+        <v>126022261</v>
       </c>
       <c r="B3" t="n">
-        <v>57657</v>
+        <v>98361</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>70</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -816,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549046</v>
+        <v>549227</v>
       </c>
       <c r="R3" t="n">
-        <v>6943812</v>
+        <v>6943821</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,11 +851,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,37 +877,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126022283</v>
+        <v>126020940</v>
       </c>
       <c r="B4" t="n">
-        <v>98361</v>
+        <v>92535</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -922,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549248</v>
+        <v>549196</v>
       </c>
       <c r="R4" t="n">
-        <v>6943846</v>
+        <v>6943799</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,37 +978,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126022261</v>
+        <v>126019996</v>
       </c>
       <c r="B5" t="n">
-        <v>98361</v>
+        <v>57657</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>70</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1023,10 +1018,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>549227</v>
+        <v>549046</v>
       </c>
       <c r="R5" t="n">
-        <v>6943821</v>
+        <v>6943812</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1059,6 +1054,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -3027,10 +3027,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126021627</v>
+        <v>126023512</v>
       </c>
       <c r="B25" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3038,34 +3038,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>549225</v>
+        <v>549050</v>
       </c>
       <c r="R25" t="n">
-        <v>6943798</v>
+        <v>6943946</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3098,6 +3103,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3124,49 +3134,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126023135</v>
+        <v>126021627</v>
       </c>
       <c r="B26" t="n">
-        <v>92535</v>
+        <v>78980</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>549141</v>
+        <v>549225</v>
       </c>
       <c r="R26" t="n">
-        <v>6943883</v>
+        <v>6943798</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3199,11 +3205,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3230,38 +3231,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126023512</v>
+        <v>126023135</v>
       </c>
       <c r="B27" t="n">
-        <v>57657</v>
+        <v>92535</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3270,10 +3270,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>549050</v>
+        <v>549141</v>
       </c>
       <c r="R27" t="n">
-        <v>6943946</v>
+        <v>6943883</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 24054-2025 artfynd.xlsx
+++ b/artfynd/A 24054-2025 artfynd.xlsx
@@ -3027,10 +3027,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126023512</v>
+        <v>126021627</v>
       </c>
       <c r="B25" t="n">
-        <v>57657</v>
+        <v>78980</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3038,39 +3038,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>549050</v>
+        <v>549225</v>
       </c>
       <c r="R25" t="n">
-        <v>6943946</v>
+        <v>6943798</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3103,11 +3098,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3134,45 +3124,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126021627</v>
+        <v>126023135</v>
       </c>
       <c r="B26" t="n">
-        <v>78980</v>
+        <v>92535</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>549225</v>
+        <v>549141</v>
       </c>
       <c r="R26" t="n">
-        <v>6943798</v>
+        <v>6943883</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3205,6 +3199,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3231,37 +3230,38 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126023135</v>
+        <v>126023512</v>
       </c>
       <c r="B27" t="n">
-        <v>92535</v>
+        <v>57657</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3270,10 +3270,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>549141</v>
+        <v>549050</v>
       </c>
       <c r="R27" t="n">
-        <v>6943883</v>
+        <v>6943946</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Äldre exemplar</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
